--- a/plantillas/Plantilla_Importacion_Casos_UAT.xlsx
+++ b/plantillas/Plantilla_Importacion_Casos_UAT.xlsx
@@ -621,8 +621,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige Alta, Media o Baja (o deja la celda vacía)." type="list">
-      <formula1>"Alta,Media,Baja"</formula1>
+    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige Urgente, Alta, Media o Baja (o deja la celda vacía)." type="list">
+      <formula1>"Urgente,Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Alta, Media o Baja. Opcional.</t>
+          <t>Urgente, Alta, Media o Baja. Opcional.</t>
         </is>
       </c>
     </row>
